--- a/lang/en/headTags.xlsx
+++ b/lang/en/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1191</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1195</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1196">
   <si>
     <t>en</t>
   </si>
@@ -2908,6 +2908,12 @@
     <t>Shulker</t>
   </si>
   <si>
+    <t>Sift (Inspired)</t>
+  </si>
+  <si>
+    <t>Sift (Vanilla)</t>
+  </si>
+  <si>
     <t>Silent Hill</t>
   </si>
   <si>
@@ -3373,6 +3379,9 @@
     <t>ULTRAKILL</t>
   </si>
   <si>
+    <t>Umamusume</t>
+  </si>
+  <si>
     <t>Umineko - When They Cry</t>
   </si>
   <si>
@@ -3521,6 +3530,9 @@
   </si>
   <si>
     <t>Winter</t>
+  </si>
+  <si>
+    <t>Winter Drop</t>
   </si>
   <si>
     <t>Witcher</t>
@@ -3939,7 +3951,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1191"/>
+  <dimension ref="A1:B1195"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -13474,8 +13486,40 @@
         <v>1191</v>
       </c>
     </row>
+    <row r="1192" spans="1:2">
+      <c r="A1192" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B1192" t="s">
+        <v>1192</v>
+      </c>
+    </row>
+    <row r="1193" spans="1:2">
+      <c r="A1193" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B1193" t="s">
+        <v>1193</v>
+      </c>
+    </row>
+    <row r="1194" spans="1:2">
+      <c r="A1194" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B1194" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:2">
+      <c r="A1195" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B1195" t="s">
+        <v>1195</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1191"/>
+  <autoFilter ref="A1:B1195"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
